--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488025_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488025_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9854</v>
+        <v>2.5561</v>
       </c>
       <c r="E2" t="n">
-        <v>2.84</v>
+        <v>2.4949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1454</v>
+        <v>0.0611</v>
       </c>
       <c r="G2" t="n">
         <v>2.2034</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2889</v>
+        <v>-0.1404</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3047</v>
+        <v>-0.0403</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2998</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3372</v>
+        <v>0.3954</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2456</v>
+        <v>1.4723</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9084</v>
+        <v>-1.0768</v>
       </c>
       <c r="G4" t="n">
         <v>1.0085</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3134</v>
+        <v>0.3716</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.756</v>
+        <v>-0.5293</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0694</v>
+        <v>0.901</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3811</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0771</v>
+        <v>-0.2018</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6681</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7452</v>
+        <v>-0.2018</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2455</v>
+        <v>-0.2018</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1211</v>
+        <v>-0.2018</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1244</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5984</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5984</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3529</v>
+        <v>-0.2018</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4774</v>
+        <v>-0.2018</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1244</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8821</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9215</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0393</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2334</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2018</v>
+        <v>-0.4499</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.2793</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2018</v>
+        <v>0.8294</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2018</v>
+        <v>-0.2455</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2018</v>
+        <v>-0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.1244</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.5984</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.5984</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2018</v>
+        <v>0.3529</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2018</v>
+        <v>0.4774</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.1244</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3552</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0449</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2334</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.2334</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6573</v>
+        <v>-0.9848</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7376</v>
+        <v>-0.9808</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0803</v>
+        <v>-0.004</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8228</v>
@@ -1000,13 +1000,13 @@
         <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0267</v>
+        <v>0.6992</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1727</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8539</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.337</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.832</v>
+        <v>-1.1095</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9777</v>
+        <v>0.6721</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8097</v>
+        <v>-1.7816</v>
       </c>
       <c r="G8" t="n">
         <v>0.0958</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.1964</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4295</v>
+        <v>0.1239</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3484</v>
+        <v>-0.3203</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SENZI KITAMBO</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1476</v>
+        <v>-1.9715</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9458</v>
+        <v>-1.7678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7982</v>
+        <v>-0.2036</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2565</v>
+        <v>-0.838</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3292</v>
+        <v>0.5472</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9273</v>
+        <v>-1.3852</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8943</v>
+        <v>1.794</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1827</v>
+        <v>1.0631</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.077</v>
+        <v>0.731</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3622</v>
+        <v>-2.632</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5119</v>
+        <v>-0.5158</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8503</v>
+        <v>-2.1162</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>-4.3609</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-6.9378</v>
       </c>
       <c r="R9" t="n">
         <v>2.5769</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1462</v>
+        <v>-0.4864</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8184</v>
+        <v>-0.5119</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9646</v>
+        <v>0.0255</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3591</v>
+        <v>3.7139</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7403</v>
+        <v>3.8879</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3811</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>E. SENZI KITAMBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2159</v>
+        <v>-2.679</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1776</v>
+        <v>-2.7191</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0382</v>
+        <v>0.0401</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1252</v>
+        <v>-3.2565</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2313</v>
+        <v>-0.3292</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3564</v>
+        <v>-2.9273</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.8943</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3159</v>
+        <v>0.1827</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5586</v>
+        <v>-1.077</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2506</v>
+        <v>-2.3622</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5472</v>
+        <v>-0.5119</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.8503</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3964</v>
+        <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2889</v>
+        <v>0.6148</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>-0.5917</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0231</v>
+        <v>1.2065</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>0.3591</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>-1.3811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3814</v>
+        <v>-2.8031</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5038</v>
+        <v>-1.8491</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.954</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.838</v>
+        <v>-1.1252</v>
       </c>
       <c r="H11" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.3564</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.8745000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.3159</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.5586</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.2506</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.5472</v>
       </c>
-      <c r="I11" t="n">
-        <v>-1.3852</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.0631</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-2.632</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.5158</v>
-      </c>
       <c r="O11" t="n">
-        <v>-2.1162</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3609</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.9378</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5769</v>
+        <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8963</v>
+        <v>0.1238</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2479</v>
+        <v>0.0165</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6484</v>
+        <v>0.1073</v>
       </c>
       <c r="V11" t="n">
-        <v>3.7139</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8879</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.174</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9512</v>
+        <v>-3.1154</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0345</v>
+        <v>-3.4233</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0833</v>
+        <v>0.3079</v>
       </c>
       <c r="G12" t="n">
         <v>1.1284</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7276</v>
+        <v>0.1082</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0608</v>
+        <v>-0.4495</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3332</v>
+        <v>0.5578</v>
       </c>
       <c r="V12" t="n">
         <v>0.6036</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.876800000000001</v>
+        <v>-8.252800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.893400000000002</v>
+        <v>-5.2694</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9832</v>
+        <v>-2.9833</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9430000000000001</v>
+        <v>-0.9429999999999996</v>
       </c>
       <c r="H13" t="n">
         <v>2.367</v>
@@ -1468,10 +1468,10 @@
         <v>12.8844</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8255999999999999</v>
+        <v>1.4496</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3667</v>
+        <v>-1.7425</v>
       </c>
       <c r="U13" t="n">
         <v>3.1923</v>
@@ -1483,7 +1483,7 @@
         <v>9.108700000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.956700000000001</v>
+        <v>-7.9567</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6631</v>
+        <v>5.2038</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8297</v>
+        <v>4.0335</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8334</v>
+        <v>1.1704</v>
       </c>
       <c r="G14" t="n">
         <v>1.3446</v>
@@ -1546,13 +1546,13 @@
         <v>3.9645</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5755</v>
+        <v>-0.0348</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2237</v>
+        <v>-0.02</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3518</v>
+        <v>-0.0148</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0704</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.097</v>
+        <v>4.1916</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7208</v>
+        <v>4.6189</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6238</v>
+        <v>-0.4273</v>
       </c>
       <c r="G15" t="n">
         <v>2.7274</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1479</v>
+        <v>-0.0532</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.0357</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.214</v>
+        <v>-0.0175</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2666</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.505</v>
+        <v>2.613</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4787</v>
+        <v>0.8675</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0263</v>
+        <v>1.7455</v>
       </c>
       <c r="G16" t="n">
         <v>0.5745</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6592</v>
+        <v>0.7672</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7674</v>
+        <v>0.1562</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8918</v>
+        <v>0.611</v>
       </c>
       <c r="V16" t="n">
         <v>1.866</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5595</v>
+        <v>1.8299</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5219</v>
+        <v>1.6238</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0376</v>
+        <v>0.2061</v>
       </c>
       <c r="G17" t="n">
         <v>1.4994</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1886</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.301</v>
+        <v>-0.1991</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1123</v>
+        <v>0.2808</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9405</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.376</v>
+        <v>0.1788</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8915</v>
+        <v>-0.4323</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2675</v>
+        <v>0.611</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0517</v>
+        <v>0.1391</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8666</v>
+        <v>-0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.4821</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1979</v>
+        <v>0.6671</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0014</v>
+        <v>-0.6186</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8036</v>
+        <v>1.2857</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8538</v>
+        <v>-0.528</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8652</v>
+        <v>0.2756</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0114</v>
+        <v>-0.8036</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5138</v>
+        <v>-0.2973</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2975</v>
+        <v>-0.1082</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2163</v>
+        <v>-0.1891</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4737</v>
+        <v>0.337</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4737</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0312</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.636</v>
+        <v>-2.1152</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6672</v>
+        <v>1.524</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1391</v>
+        <v>-0.4509</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.343</v>
+        <v>-0.3421</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4821</v>
+        <v>-0.1089</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6671</v>
+        <v>0.4478</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6186</v>
+        <v>-0.094</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2857</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.528</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2756</v>
+        <v>-0.2481</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8036</v>
+        <v>-0.6506</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9911</v>
+        <v>3.7662</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4449</v>
+        <v>-0.4506</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.312</v>
+        <v>-0.5807</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1329</v>
+        <v>0.1301</v>
       </c>
       <c r="V20" t="n">
-        <v>0.337</v>
+        <v>-1.4737</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.337</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9397</v>
+        <v>-0.6589</v>
       </c>
       <c r="E21" t="n">
         <v>-2.2205</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2809</v>
+        <v>1.5617</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4922</v>
@@ -2092,13 +2092,13 @@
         <v>2.5769</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4037</v>
+        <v>-0.1229</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4844</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.3615</v>
       </c>
       <c r="V21" t="n">
         <v>2.3438</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0444</v>
+        <v>-1.0671</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6245</v>
+        <v>-1.6046</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5801</v>
+        <v>0.5374</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4509</v>
+        <v>-1.0517</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3421</v>
+        <v>-1.8666</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1089</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4478</v>
+        <v>-0.1979</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.094</v>
+        <v>-1.0014</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8987000000000001</v>
+        <v>-0.8538</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2481</v>
+        <v>-0.8652</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6506</v>
+        <v>0.0114</v>
       </c>
       <c r="P22" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7662</v>
+        <v>2.3787</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9038</v>
+        <v>0.0707</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0901</v>
+        <v>-0.4156</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1863</v>
+        <v>0.4863</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4737</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7867</v>
+        <v>-1.4988</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6144</v>
+        <v>-1.4107</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1723</v>
+        <v>-0.0881</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5139</v>
@@ -2248,13 +2248,13 @@
         <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7991</v>
+        <v>-0.5112</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1011</v>
+        <v>-0.8973</v>
       </c>
       <c r="U23" t="n">
-        <v>0.302</v>
+        <v>0.3862</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4897</v>
+        <v>-2.2298</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4862</v>
+        <v>-1.2825</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0034</v>
+        <v>-0.9473</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7385</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5352</v>
+        <v>-0.2753</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8112</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.276</v>
+        <v>0.3322</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2362,16 +2362,16 @@
         <v>8.8766</v>
       </c>
       <c r="E25" t="n">
-        <v>2.983300000000002</v>
+        <v>2.983199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8935</v>
+        <v>5.8934</v>
       </c>
       <c r="G25" t="n">
         <v>0.9431</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3671</v>
+        <v>-2.367100000000001</v>
       </c>
       <c r="I25" t="n">
         <v>3.3101</v>
@@ -2392,10 +2392,10 @@
         <v>-4.2475</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.912500000000001</v>
+        <v>-5.9125</v>
       </c>
       <c r="P25" t="n">
-        <v>9.911099999999999</v>
+        <v>9.911099999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.8844</v>
@@ -2407,7 +2407,7 @@
         <v>-0.8257</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.1924</v>
+        <v>-3.1922</v>
       </c>
       <c r="U25" t="n">
         <v>2.3667</v>
